--- a/data/b2_centro/B2 Centro 06-2026.xlsx
+++ b/data/b2_centro/B2 Centro 06-2026.xlsx
@@ -4766,146 +4766,146 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>77980.60000000001</v>
+        <v>3203.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46180</v>
+        <v>46176</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>5537.52</v>
+        <v>4259.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>38000</v>
+        <v>79079.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46183</v>
+        <v>46180</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>4300</v>
+        <v>5818.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>2144.56</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2021.07</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46187</v>
+        <v>46185</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>5413.95</v>
+        <v>2031.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46188</v>
+        <v>46187</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>13441.11</v>
+        <v>5244.19</v>
       </c>
     </row>
     <row r="10">
@@ -4914,16 +4914,16 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>3527.87</v>
+        <v>13843.38</v>
       </c>
     </row>
     <row r="11">
@@ -4932,21 +4932,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1933.15</v>
+        <v>3742.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -4955,29 +4955,29 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>2110.67</v>
+        <v>1805.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>4261.41</v>
+        <v>2254.45</v>
       </c>
     </row>
     <row r="14">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>27400.21</v>
+        <v>27350.84</v>
       </c>
     </row>
     <row r="15">
@@ -5013,25 +5013,25 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>5125.4</v>
+        <v>5152.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2230.88</v>
+        <v>1474.99</v>
       </c>
     </row>
     <row r="17">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>5327.21</v>
+        <v>5534.08</v>
       </c>
     </row>
     <row r="18">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1447.46</v>
+        <v>1433.42</v>
       </c>
     </row>
   </sheetData>
